--- a/dataset/stats/Ground/France_Realistic.xlsx
+++ b/dataset/stats/Ground/France_Realistic.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,76 +425,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N105"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Rank_Info</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Сыграно игр</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Победы</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Процент побед</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Возрождения</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Наземные убийства</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Воздушные убийства</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Морские убийства</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Смерти</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Убийств за возрождение</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Убийств за смерть</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SL за игру</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>RP за игру</t>
         </is>
@@ -491,70 +508,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>fr_leopard_2a4nl_les</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Leopard2(OTCo)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>515,308</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>230,571</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>44.7%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>672,952</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>863,165</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>5,838</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>613,089</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21,273</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>1,719</t>
         </is>
@@ -563,70 +585,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>fr_jaguar_ebrc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>EBRCJaguar</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.0#2</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>495,601</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>244,906</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>49.4%</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>599,793</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>487,076</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>55,603</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>551,678</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>5,655</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>602</t>
         </is>
@@ -635,70 +662,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>fr_amx_m4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>AMXM4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>458,426</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>247,698</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>54.0%</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>533,882</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>665,267</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1,498</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>462,853</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>1.44</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>7,031</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>441</t>
         </is>
@@ -707,70 +739,75 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>fr_somua_sm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>SomuaSM</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#4</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>429,284</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>251,976</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>58.7%</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>546,951</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>912,926</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>3,625</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>481,376</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1.68</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>25,248</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>1,532</t>
         </is>
@@ -779,70 +816,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>fr_msc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>MSC</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ранг 7БР 11.0#5</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>390,812</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>182,425</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>46.7%</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>460,774</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>554,614</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>4,538</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>415,040</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>8,081</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>804</t>
         </is>
@@ -851,70 +893,75 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>fr_amx_50_surbaisse</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>AMX-50Surbaissé</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#6</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>362,234</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>201,739</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>55.7%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>399,123</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>526,255</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>2,633</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>335,817</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1.57</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>7,937</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>533</t>
         </is>
@@ -923,70 +970,75 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>fr_amx_30_super</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>AMX-30Super</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#7</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>337,436</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>176,932</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>424,114</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>603,709</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>4,129</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>382,119</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1.59</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>20,325</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>1,481</t>
         </is>
@@ -995,70 +1047,75 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>fr_arl_44</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ARL-44</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.3#8</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>305,298</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>156,655</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>344,167</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>340,433</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>1,223</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>294,123</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>3,944</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>302</t>
         </is>
@@ -1067,70 +1124,75 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>fr_lorraine_40t</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Lorraine40t</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#9</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>286,032</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>159,849</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>55.9%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>305,889</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>352,814</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>1,895</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>255,395</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>6,422</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>431</t>
         </is>
@@ -1139,70 +1201,75 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>fr_amx_50</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>AMX-50(TOA100)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#10</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>282,687</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>156,884</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>55.5%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>303,529</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>372,713</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>1,842</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>246,826</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>6,964</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>463</t>
         </is>
@@ -1211,70 +1278,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>fr_leclerc_s1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Leclerc</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#11</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>275,757</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>143,197</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>51.9%</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>310,875</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>393,836</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>2,009</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>281,795</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1.27</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>7,977</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>806</t>
         </is>
@@ -1283,70 +1355,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>fr_amx_30_dca</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>AMX-30SDCA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#12</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>273,374</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>127,154</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>46.5%</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>327,635</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>230,318</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>59,853</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>263,848</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>5,360</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>381</t>
         </is>
@@ -1355,70 +1432,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>fr_amx_10p</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>AMX-10P</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.3#13</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>272,169</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>127,830</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>47.0%</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>309,577</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>92,098</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>59,630</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>229,741</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>0.66</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>3,000</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>221</t>
         </is>
@@ -1427,70 +1509,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>fr_amx_13_dca_40</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>AMX-13DCA40</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#14</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>260,679</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>128,772</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>49.4%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>304,598</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>152,115</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>73,004</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>243,744</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2,527</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>219</t>
         </is>
@@ -1499,70 +1586,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>fr_amx_elc_bis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>ELCbis</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#15</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>256,687</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>134,288</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>287,806</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>224,674</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>411</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>256,009</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>4,357</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>326</t>
         </is>
@@ -1571,70 +1663,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>fr_panhard_ebr_1951</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>E.B.R.(1951)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.3#16</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>247,351</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>134,424</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>54.3%</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>268,764</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>213,824</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>237,679</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>3,665</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>300</t>
         </is>
@@ -1643,70 +1740,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>fr_amx_32_105</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>AMX-32(105)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>237,346</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>117,926</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>49.7%</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>270,158</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>257,275</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>3,697</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>235,909</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>6,127</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>463</t>
         </is>
@@ -1715,70 +1817,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>fr_leclerc_sxxi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>LeclercSXXI</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#18</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>230,321</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>121,192</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>52.6%</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>250,798</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>320,893</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1,729</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>225,106</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>7,886</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>797</t>
         </is>
@@ -1787,70 +1894,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>fr_m4a4_cn_75_50</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>M4A4(SA50)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#19</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>198,394</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>100,582</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>50.7%</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>215,917</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>194,113</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1,023</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>176,392</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>3,335</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>270</t>
         </is>
@@ -1859,70 +1971,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>fr_amx_30_1972</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>AMX-30(1972)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#20</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>195,469</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>103,827</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>53.1%</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>220,568</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>183,974</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>4,891</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>189,306</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>6,002</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>410</t>
         </is>
@@ -1931,70 +2048,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>fr_amx_13_75</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>AMX-13</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#21</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>194,936</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>104,381</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>53.5%</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>206,454</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>171,890</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>623</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>177,147</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>4,236</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>311</t>
         </is>
@@ -2003,70 +2125,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>fr_m36b2_cefeo</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>▄M36B2</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#22</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>191,917</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>94,426</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>49.2%</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>215,190</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>159,594</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>5,990</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>187,998</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>3,606</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>243</t>
         </is>
@@ -2075,70 +2202,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>fr_vcac_mephisto</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>MEPHISTO</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#23</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>183,618</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>92,033</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>50.1%</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>204,255</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>204,936</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1,382</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>177,387</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>1.16</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>6,158</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>445</t>
         </is>
@@ -2147,70 +2279,75 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>fr_amx_13_fl_11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>AMX-13(FL11)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.3#24</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>179,599</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>98,417</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>54.8%</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>199,904</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>170,908</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>461</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>176,055</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>2,680</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>269</t>
         </is>
@@ -2219,70 +2356,75 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>fr_leclerc_azur</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>LeclercAZUR</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#25</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>179,163</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>94,483</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>52.7%</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>197,285</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>241,923</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1,435</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>179,852</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>7,792</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>767</t>
         </is>
@@ -2291,70 +2433,75 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>fr_amx_40</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>AMX-40</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#26</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>176,419</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>84,509</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>47.9%</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>201,153</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>211,362</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>2,561</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>176,547</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>7,127</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>611</t>
         </is>
@@ -2363,70 +2510,75 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>fr_arl_44_acl1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>ARL-44(ACL-1)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#27</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>169,714</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>95,645</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>56.4%</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>188,954</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>171,824</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>158,920</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>3,476</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>295</t>
         </is>
@@ -2435,70 +2587,75 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>fr_vextra_105</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Vextra105</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.0#28</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>167,833</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>81,175</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>48.4%</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>184,695</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>146,768</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>972</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>165,487</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>4,760</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>455</t>
         </is>
@@ -2507,70 +2664,75 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>fr_amd_35_kwk39</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>AMD.35(PaK)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#29</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>165,610</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>94,774</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>57.2%</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>188,404</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>198,441</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>166,614</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>1.20</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>1,115</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>229</t>
         </is>
@@ -2579,70 +2741,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>fr_leclerc_s2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>LeclercS2</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#30</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>163,542</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>83,846</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>176,992</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>206,507</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1,233</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>157,208</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>7,258</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>713</t>
         </is>
@@ -2651,70 +2818,75 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>fr_aml_90</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>AML-90</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#31</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>161,559</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>90,376</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>55.9%</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>172,539</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>109,855</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1,317</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>150,060</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>0.74</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>4,217</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>329</t>
         </is>
@@ -2723,70 +2895,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>fr_vbci</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>VBCI</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#32</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>149,830</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>78,842</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>52.6%</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>170,847</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>140,289</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>7,719</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>149,977</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>5,380</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>465</t>
         </is>
@@ -2795,70 +2972,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>fr_leopard_2a4nl</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Leopard2A4NL</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Ранг 7БР 10.7#33</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>141,447</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>63,670</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>157,690</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>159,093</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1,528</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>136,252</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>1.02</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>6,742</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>605</t>
         </is>
@@ -2867,70 +3049,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>fr_m4a4_sherman</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>▄M4A4</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Ранг 3БР 3.7#34</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>138,790</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>79,918</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>57.6%</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>151,226</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>199,157</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>1,849</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>124,103</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>3,387</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>319</t>
         </is>
@@ -2939,70 +3126,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>fr_m10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>▄M10GMC</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.3#35</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>138,246</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>75,224</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>54.4%</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>152,344</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>157,725</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>4,446</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>128,434</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>1.26</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>2,606</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>237</t>
         </is>
@@ -3011,70 +3203,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>fr_vbci2_mct30</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>VBCI-2(MCT30)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#36</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>136,120</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>70,154</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>51.5%</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>160,689</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>142,059</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>7,326</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>142,533</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>13,503</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>1,167</t>
         </is>
@@ -3083,70 +3280,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>fr_m26_pershing</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>▄M26</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.7#37</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>135,475</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>67,835</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>50.1%</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>146,414</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>124,280</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>3,563</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>117,974</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0.87</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>4,839</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>309</t>
         </is>
@@ -3155,70 +3357,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>fr_m4a1_sherman</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>▄M4A1</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.3#38</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>132,571</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>76,103</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>57.4%</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>147,486</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>193,665</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>5,292</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>122,500</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>1.62</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>2,845</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>295</t>
         </is>
@@ -3227,70 +3434,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>fr_marder_df_105</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>DF105</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#39</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>132,025</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>72,211</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>54.7%</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>144,794</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>138,776</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>1,021</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>126,887</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>1.10</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>5,189</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>415</t>
         </is>
@@ -3299,70 +3511,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>fr_amx_30_b2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>AMX-30B2</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#40</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>131,582</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>67,385</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>146,768</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>141,836</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>2,939</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>123,384</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>6,137</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>432</t>
         </is>
@@ -3371,70 +3588,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>fr_tpk_641_vpc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>TPK6.41</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#41</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>129,093</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>60,641</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>47.0%</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>146,060</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>17,785</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>67,508</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>105,251</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0.58</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>2,324</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>179</t>
         </is>
@@ -3443,70 +3665,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>fr_cv_9035_nl</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>CV9035NL</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#42</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>128,134</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>63,555</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>49.6%</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>147,021</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>123,868</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>3,045</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>128,970</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>5,654</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>523</t>
         </is>
@@ -3515,70 +3742,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>fr_amx_10rc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>AMX-10RC</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#43</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>127,864</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>67,728</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>53.0%</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>141,201</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>118,974</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1,552</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>121,869</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>4,651</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>390</t>
         </is>
@@ -3587,70 +3819,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>fr_amd_35</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>AMD.35</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#44</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>127,555</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>63,275</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>49.6%</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>153,925</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>129,864</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1,951</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>138,189</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>0.86</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>200</t>
         </is>
@@ -3659,70 +3896,75 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>fr_amx_32</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>AMX-32</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.7#45</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>126,388</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>63,065</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>49.9%</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>143,069</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>151,449</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1,913</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>123,964</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>1.24</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>6,772</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>515</t>
         </is>
@@ -3731,70 +3973,75 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>fr_amx_30_auf_1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>AuF1</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#46</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>125,896</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>63,586</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>50.5%</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>138,304</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>84,120</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>5,223</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>115,467</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>4,189</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>260</t>
         </is>
@@ -3803,70 +4050,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>fr_lorraine_100</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>CALorraine</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#47</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>124,435</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>61,008</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>49.0%</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>135,457</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>97,096</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>116,524</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>4,096</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>264</t>
         </is>
@@ -3875,70 +4127,75 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>fr_amx_50_foch</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>AMX-50Foch</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#48</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>121,560</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>65,527</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>53.9%</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>136,137</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>133,579</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>111,015</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>7,045</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>447</t>
         </is>
@@ -3947,70 +4204,75 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>fr_amx_30_b2_brenus</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>AMX-30B2BRENUS</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#49</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>118,675</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>62,603</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>52.8%</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>131,208</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>142,895</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>110,562</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>7,000</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>510</t>
         </is>
@@ -4019,70 +4281,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>fr_amx_vtt_dca</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>VTTDCA</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#50</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>117,853</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>57,573</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>48.9%</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>132,638</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>18,078</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>55,390</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>92,718</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>1,062</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>155</t>
         </is>
@@ -4091,70 +4358,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>fr_m4a3_105_sherman</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>▄M4A3(105)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.0#51</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>117,543</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>65,642</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>55.8%</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>132,982</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>140,002</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>4,652</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>110,890</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>1.09</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>2,260</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>268</t>
         </is>
@@ -4163,70 +4435,75 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>fr_mars_15</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>MARS15</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#52</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>105,552</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>55,265</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>116,437</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>93,741</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>757</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>100,956</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>4,535</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>368</t>
         </is>
@@ -4235,70 +4512,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>fr_samp_t_fcs</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>FSAFSAMP/T(Mamba)(TADS)</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#53</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>98,284</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>51,428</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>109,210</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>113,295</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>83,667</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>1.04</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>4,823</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>344</t>
         </is>
@@ -4307,70 +4589,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>fr_amx_13_90</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>AMX-13-90</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#54</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>91,919</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>51,010</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>55.5%</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>97,527</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>89,352</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>81,327</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>4,950</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>382</t>
         </is>
@@ -4379,70 +4666,75 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>fr_m44</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>▄M44</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#55</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>91,558</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>47,005</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>51.3%</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>99,602</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>75,911</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>2,946</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>84,848</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>2,322</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>202</t>
         </is>
@@ -4451,70 +4743,75 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>fr_m4a3e2_sherman_jumbo</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>▄M4A3E2</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.7#56</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>91,051</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>47,650</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>52.3%</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>100,328</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>108,311</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>2,821</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>83,696</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>1.11</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>5,117</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>356</t>
         </is>
@@ -4523,70 +4820,75 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>fr_vab_santal</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>SANTAL</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>Ранг 6БР 9.3#57</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>87,428</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>39,808</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>45.5%</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>105,429</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>65,209</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>64,871</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>0.62</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>3,446</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>240</t>
         </is>
@@ -4595,70 +4897,75 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>fr_m3a3_stuart</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>▄M3A3Stuart</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#58</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>86,628</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>48,936</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>56.5%</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>94,223</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>80,078</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>2,787</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>78,646</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>1,446</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>246</t>
         </is>
@@ -4667,70 +4974,75 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>fr_crusader_mk_2</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>▄CrusaderMk.II</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#59</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>83,619</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>46,912</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>56.1%</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>90,134</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>70,998</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1,495</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>75,999</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>0.80</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>1,306</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>220</t>
         </is>
@@ -4739,70 +5051,75 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>fr_cckw_353_bofors</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>CCKW353AA</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#60</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>79,962</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>40,905</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>51.2%</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>91,629</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>53,560</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>19,267</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>70,836</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>913</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>158</t>
         </is>
@@ -4811,70 +5128,75 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>fr_panhard_ebr_1954</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>E.B.R.(1954)</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#61</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>75,493</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>43,009</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>57.0%</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>90,872</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>121,680</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>321</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>81,636</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>1.34</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>12,071</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>907</t>
         </is>
@@ -4883,70 +5205,75 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>fr_amx_30_roland</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Roland1</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>Ранг 7БР 9.7#62</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>72,877</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>30,058</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>41.2%</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>99,843</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>8,802</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>55,919</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>68,584</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>3,719</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>289</t>
         </is>
@@ -4955,70 +5282,75 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>fr_bat_chat_25t</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>Char25t</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#63</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>71,390</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>39,687</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>55.6%</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>77,149</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>97,746</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>64,139</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>1.28</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>447</t>
         </is>
@@ -5027,70 +5359,75 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>fr_amx_30_ACRA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>AMX-30ACRA</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#64</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>69,528</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>35,298</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>50.8%</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>76,070</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>58,152</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>2,006</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>62,958</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>5,255</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>375</t>
         </is>
@@ -5099,70 +5436,75 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>fr_m4a1_sherman_fl_10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>M4A1(FL10)</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>Ранг 3БР 5.0#65</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>68,834</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>38,639</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>56.1%</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>85,787</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>113,857</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>75,431</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>1.33</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>1.51</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>13,647</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>940</t>
         </is>
@@ -5171,70 +5513,75 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>fr_sk105_a2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>SK-105A2</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.7#66</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>66,207</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>35,967</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>54.3%</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>72,949</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>88,186</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>62,348</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>5,933</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>499</t>
         </is>
@@ -5243,70 +5590,75 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>fr_amx_10m_acra</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>AMX-10M</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.3#67</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>65,431</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>34,409</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>52.6%</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>74,505</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>58,713</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>4,914</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>63,612</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>0.85</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>5,371</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>354</t>
         </is>
@@ -5315,70 +5667,75 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>fr_amc_35</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>AMC.35(ACG.1)</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#68</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>63,256</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>30,177</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>47.7%</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>68,000</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>41,615</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1,168</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>58,386</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>0.63</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>310</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>135</t>
         </is>
@@ -5387,70 +5744,75 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>fr_leopard_2a6nl</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>Leopard2A6NL</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#69</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>61,799</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>32,395</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>52.4%</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>67,708</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>82,823</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>505</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>59,858</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>7,561</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>738</t>
         </is>
@@ -5459,70 +5821,75 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>fr_hotchkiss_h39</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>H.39</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#70</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>60,886</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>27,915</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>45.8%</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>69,836</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>50,893</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>2,236</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>56,420</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>167</t>
         </is>
@@ -5531,70 +5898,75 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>fr_crotale_ng</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>▄ItO90M</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.0#71</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>60,343</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>28,207</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>46.7%</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>82,365</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>6,679</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>53,493</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>58,240</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>1.03</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>4,615</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>332</t>
         </is>
@@ -5603,70 +5975,75 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>fr_leopard_2a5nl</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Leopard2A5NL</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.3#72</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>58,212</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>29,728</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>51.1%</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>65,571</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>69,406</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>57,470</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>6,846</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>630</t>
         </is>
@@ -5675,70 +6052,75 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>fr_m46_patton</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>▄M46</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#73</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>54,611</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>30,907</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>56.6%</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>66,696</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>91,904</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>1,648</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>57,406</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>20,384</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>1,228</t>
         </is>
@@ -5747,70 +6129,75 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>fr_m55</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>▄M55</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.0#74</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>50,655</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>26,249</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>51.8%</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>56,342</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>47,855</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>1,759</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>47,303</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>0.88</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>3,092</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>251</t>
         </is>
@@ -5819,70 +6206,75 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>fr_somua_s35</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>S.35</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#75</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>50,487</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>24,392</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>48.3%</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>54,280</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>49,331</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1,136</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>44,032</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>0.93</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>179</t>
         </is>
@@ -5891,70 +6283,75 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>fr_b1_bis</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>B1bis</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#76</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>47,087</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>24,518</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>52.1%</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>51,640</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>42,334</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>40,576</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>0.83</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>1,372</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>221</t>
         </is>
@@ -5963,70 +6360,75 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>fr_lorraine_37l</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Lorraine37L</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#77</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>42,188</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>21,059</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>49.9%</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>46,163</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>51,429</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>37,797</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>1.12</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>1.37</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>789</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>186</t>
         </is>
@@ -6035,70 +6437,75 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>fr_citroen_kegresse_p4t</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>P.7.TAA</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#78</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>41,719</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>18,249</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>43.7%</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>46,366</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>9,687</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>16,398</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>32,070</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>105</t>
         </is>
@@ -6107,70 +6514,75 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>fr_amx_13_chaffee</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>AMX-13-M24</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.7#79</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>38,375</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>23,306</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>60.7%</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>46,189</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>68,851</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>1,497</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>40,970</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>1.72</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>7,763</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>836</t>
         </is>
@@ -6179,70 +6591,75 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>fr_char_2c</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>2C</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.3#80</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>33,420</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>17,799</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>53.3%</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>36,411</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>49,214</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>28,324</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>1.36</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>1.75</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>1,913</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>257</t>
         </is>
@@ -6251,70 +6668,75 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>fr_marder_clovis</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>CLOVIS</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#81</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>32,957</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>18,559</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>56.3%</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>41,590</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>47,978</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1,114</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>37,134</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>16,346</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>1,281</t>
         </is>
@@ -6323,70 +6745,75 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>fr_amx_30</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>AMX-30</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#82</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>32,878</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>17,555</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>53.4%</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>38,590</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>34,239</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>32,836</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>15,915</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>1,061</t>
         </is>
@@ -6395,70 +6822,75 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>fr_amr_35_zt3</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>AMR.35ZT3</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#83</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>31,566</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>14,813</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>46.9%</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>34,140</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>18,347</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>425</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>29,562</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>0.55</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>0.64</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>362</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>125</t>
         </is>
@@ -6467,70 +6899,75 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>fr_amx_50_1950</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>AMX-50(TO90/930)</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Ранг 5БР 8.0#84</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>28,191</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>16,306</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>57.8%</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>33,855</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>51,423</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>389</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>29,759</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>1.74</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>21,583</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>1,335</t>
         </is>
@@ -6539,70 +6976,75 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>fr_pzkpfw_V_panther_dauphine</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>Panther""Dauphiné</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#85</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>27,857</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>15,121</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>54.3%</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>34,056</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>48,270</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>153</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>29,605</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>1.64</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>18,099</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>1,113</t>
         </is>
@@ -6611,70 +7053,75 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>fr_renault_d2</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>D2</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.3#86</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>21,680</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>10,581</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>48.8%</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>23,125</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>24,273</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>579</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>17,810</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>1.07</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>1.40</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>732</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>195</t>
         </is>
@@ -6683,70 +7130,75 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>fr_amx_13_75_ss11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>AMX-13(SS.11)</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Ранг 4БР 7.0#87</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>20,137</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>11,170</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>55.5%</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>23,138</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>23,151</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>20,273</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>12,385</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>917</t>
         </is>
@@ -6755,70 +7207,75 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>fr_amx_13_hot</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>AMX-13(HOT)</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Ранг 6БР 8.3#88</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>19,868</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>10,319</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>51.9%</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>21,761</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>13,937</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>18,574</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>0.65</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>3,978</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>332</t>
         </is>
@@ -6827,70 +7284,75 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>fr_somua_sau40</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>SAu40</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#89</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>17,458</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>8,604</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>49.3%</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>19,035</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>19,145</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>145</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>15,694</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>958</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>175</t>
         </is>
@@ -6899,70 +7361,75 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>fr_panhard_ebr_1963</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>E.B.R.(1963)</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#90</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>17,402</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>10,391</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>59.7%</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>19,231</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>18,505</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>181</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>16,392</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>1.14</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>13,228</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>980</t>
         </is>
@@ -6971,70 +7438,75 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>fr_renault_r39</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>R.35(SA38)</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#91</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>14,194</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>6,390</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>45.0%</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>14,929</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>10,411</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>392</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>11,466</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>146</t>
         </is>
@@ -7043,70 +7515,75 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>fr_b1_ter</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>B1ter</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Ранг 2БР 2.7#92</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>13,940</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>8,282</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>59.4%</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>16,322</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>22,985</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>204</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>13,156</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>1.42</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>1.76</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>5,029</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>785</t>
         </is>
@@ -7115,70 +7592,75 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>fr_char_2c_bis</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>2Cbis</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#93</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>13,103</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>6,785</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>51.8%</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>15,501</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>16,271</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>12,403</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>1.32</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>2,467</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>512</t>
         </is>
@@ -7187,70 +7669,75 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>fr_amc_34</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>AMC.34YR</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#94</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>10,235</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>4,520</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>44.2%</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>10,881</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>4,257</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t>9,426</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>0.47</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>107</t>
         </is>
@@ -7259,70 +7746,75 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>fr_fcm_36</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>FCM.36</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#95</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>8,382</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>3,819</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="F96" t="inlineStr">
         <is>
           <t>45.6%</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>8,899</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>3,452</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t>7,506</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>289</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>131</t>
         </is>
@@ -7331,70 +7823,75 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>fr_lvt_bofors</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>LVT-4/40</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>Ранг 2БР 3.7#96</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>8,243</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>5,028</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>61.0%</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>9,438</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>7,275</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>2,103</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>7,625</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>3,096</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>558</t>
         </is>
@@ -7403,70 +7900,75 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>fr_saint_chamond</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>St-Chamond</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#97</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>7,952</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>3,920</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>49.3%</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>8,757</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>8,268</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>109</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t>7,175</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>0.96</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>163</t>
         </is>
@@ -7475,70 +7977,75 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>fr_hotchkiss_h35</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>H.35</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#98</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>6,099</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>2,627</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>43.1%</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>6,358</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>1,968</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>5,195</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>0.34</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>109</t>
         </is>
@@ -7547,70 +8054,75 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>fr_amd_35_sa35</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>AMD.35(SA35)</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.7#99</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>4,894</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>2,681</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="F100" t="inlineStr">
         <is>
           <t>54.8%</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>5,744</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>5,420</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>5,195</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>1.05</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>1,941</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>489</t>
         </is>
@@ -7619,70 +8131,75 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>fr_amx_50_surblinde</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>AMX-50Surblindé</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Ранг 5БР 7.7#100</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>4,346</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>2,807</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>64.6%</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>5,444</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>11,476</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t>4,686</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>2.13</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>2.47</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>14,417</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>1,206</t>
         </is>
@@ -7691,70 +8208,75 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>fr_lorraine_155</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>Lorraine155Mle.50</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Ранг 3БР 4.3#101</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>3,856</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>2,088</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="F102" t="inlineStr">
         <is>
           <t>54.1%</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>4,554</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>4,680</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t>4,059</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>1.22</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>9,146</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>643</t>
         </is>
@@ -7763,70 +8285,75 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>fr_hotchkiss_h39_cambronne</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>H.39""Cambronne</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>Ранг 1БР 1.0#102</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>3,179</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>1,521</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>47.8%</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>3,667</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>3,598</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t>3,072</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>1,249</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>364</t>
         </is>
@@ -7835,44 +8362,44 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>fr_amx_elc_901</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>ELC901</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Ранг 4БР 6.0#103</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7880,25 +8407,30 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>44,305</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>2,956</t>
         </is>
@@ -7907,19 +8439,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>fr_samp_t_launcher</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>FSAFSAMP/T(Mamba)(TEL)</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Ранг 8БР 12.7#104</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -7971,6 +8503,11 @@
         </is>
       </c>
       <c r="N105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
